--- a/files/studi-literatur.xlsx
+++ b/files/studi-literatur.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\KERJOAN\Skripsi\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\my-website\academic-kickstart-master\rameliaz.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DD3F0D-5CF5-4A27-8683-B045F0BEB45E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970B4E7B-2588-477A-8406-30F4DD8AA7BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{70AE78E0-2689-42C6-A469-EE2B65E74026}"/>
   </bookViews>
@@ -356,9 +356,6 @@
     <t>It was assumed that individuals would be less likely to drop hateful comments and therefore, more likely to conform to the group norms when the abhorrent comments are moderately censored.</t>
   </si>
   <si>
-    <t>The authors testes their hypotheses by performing linear-mixed model, where topics and pictures as random factors and no fixed factor.</t>
-  </si>
-  <si>
     <t>180 participants were included in this study, and more than a half (55%) were women, mostly (42%) aged between 25-34 y.o., and mostly (29%) were students.</t>
   </si>
   <si>
@@ -378,6 +375,9 @@
   </si>
   <si>
     <t>There was not enough evidence to conclude that reactance is a cause of a more prevalent hate speech (in extremely censored condition) as it requires two requirements; participants must believe that their freedom is threatened and perceive that this freedom is salient to them. Both were missing in the research design.</t>
+  </si>
+  <si>
+    <t>The authors tested their hypotheses by performing linear-mixed model, where topics and pictures as random factors and no fixed factor.</t>
   </si>
 </sst>
 </file>
@@ -1240,34 +1240,34 @@
         <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>44</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>48</v>
+      </c>
+      <c r="K11" s="4" t="s">
+        <v>51</v>
+      </c>
+      <c r="L11" s="4" t="s">
+        <v>47</v>
+      </c>
+      <c r="M11" s="4" t="s">
         <v>45</v>
       </c>
-      <c r="J11" s="4" t="s">
-        <v>49</v>
-      </c>
-      <c r="K11" s="4" t="s">
-        <v>44</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>48</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>46</v>
-      </c>
       <c r="N11" s="4" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/files/studi-literatur.xlsx
+++ b/files/studi-literatur.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\my-website\academic-kickstart-master\rameliaz.github.io\files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{970B4E7B-2588-477A-8406-30F4DD8AA7BB}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839C1AA1-0D1F-424C-A26B-A5ECE986B128}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{70AE78E0-2689-42C6-A469-EE2B65E74026}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{70AE78E0-2689-42C6-A469-EE2B65E74026}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>

--- a/files/studi-literatur.xlsx
+++ b/files/studi-literatur.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\my-website\academic-kickstart-master\rameliaz.github.io\files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Drive\KERJOAN\Skripsi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{839C1AA1-0D1F-424C-A26B-A5ECE986B128}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7DD3F0D-5CF5-4A27-8683-B045F0BEB45E}" xr6:coauthVersionLast="45" xr6:coauthVersionMax="45" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" xr2:uid="{70AE78E0-2689-42C6-A469-EE2B65E74026}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12720" activeTab="1" xr2:uid="{70AE78E0-2689-42C6-A469-EE2B65E74026}"/>
   </bookViews>
   <sheets>
     <sheet name="template" sheetId="1" r:id="rId1"/>
@@ -356,6 +356,9 @@
     <t>It was assumed that individuals would be less likely to drop hateful comments and therefore, more likely to conform to the group norms when the abhorrent comments are moderately censored.</t>
   </si>
   <si>
+    <t>The authors testes their hypotheses by performing linear-mixed model, where topics and pictures as random factors and no fixed factor.</t>
+  </si>
+  <si>
     <t>180 participants were included in this study, and more than a half (55%) were women, mostly (42%) aged between 25-34 y.o., and mostly (29%) were students.</t>
   </si>
   <si>
@@ -375,9 +378,6 @@
   </si>
   <si>
     <t>There was not enough evidence to conclude that reactance is a cause of a more prevalent hate speech (in extremely censored condition) as it requires two requirements; participants must believe that their freedom is threatened and perceive that this freedom is salient to them. Both were missing in the research design.</t>
-  </si>
-  <si>
-    <t>The authors tested their hypotheses by performing linear-mixed model, where topics and pictures as random factors and no fixed factor.</t>
   </si>
 </sst>
 </file>
@@ -1240,34 +1240,34 @@
         <v>41</v>
       </c>
       <c r="E11" s="4" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>43</v>
       </c>
       <c r="G11" s="4" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="H11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="I11" s="4" t="s">
+        <v>45</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>49</v>
+      </c>
+      <c r="K11" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="L11" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="K11" s="4" t="s">
+      <c r="M11" s="4" t="s">
+        <v>46</v>
+      </c>
+      <c r="N11" s="4" t="s">
         <v>51</v>
-      </c>
-      <c r="L11" s="4" t="s">
-        <v>47</v>
-      </c>
-      <c r="M11" s="4" t="s">
-        <v>45</v>
-      </c>
-      <c r="N11" s="4" t="s">
-        <v>50</v>
       </c>
     </row>
   </sheetData>
